--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N6_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N6_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>85.44512243062665</v>
+        <v>13.88483239497683</v>
       </c>
       <c r="D2" t="n">
-        <v>4.174159928789388</v>
+        <v>0.6783009884282756</v>
       </c>
       <c r="E2" t="n">
-        <v>22.03830187623384</v>
+        <v>3.581224054887999</v>
       </c>
       <c r="F2" t="n">
-        <v>12.51736479994342</v>
+        <v>2.034071779990805</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.64862847849054</v>
+        <v>9.855402127754713</v>
       </c>
       <c r="D3" t="n">
-        <v>37.04986191031885</v>
+        <v>6.020602560426814</v>
       </c>
       <c r="E3" t="n">
-        <v>22.03830187623384</v>
+        <v>3.581224054887999</v>
       </c>
       <c r="F3" t="n">
-        <v>12.51736479994342</v>
+        <v>2.034071779990805</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>68.19307381630411</v>
+        <v>11.08137449514942</v>
       </c>
       <c r="D4" t="n">
-        <v>35.6931365951495</v>
+        <v>5.800134696711793</v>
       </c>
       <c r="E4" t="n">
-        <v>22.03830187623384</v>
+        <v>3.581224054887999</v>
       </c>
       <c r="F4" t="n">
-        <v>12.51736479994342</v>
+        <v>2.034071779990805</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>43.22246624701246</v>
+        <v>7.023650765139524</v>
       </c>
       <c r="D5" t="n">
-        <v>7.381510222923553</v>
+        <v>1.199495411225077</v>
       </c>
       <c r="E5" t="n">
-        <v>22.03830187623384</v>
+        <v>3.581224054887999</v>
       </c>
       <c r="F5" t="n">
-        <v>12.51736479994342</v>
+        <v>2.034071779990805</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.46553094121722</v>
+        <v>9.500648777947799</v>
       </c>
       <c r="D6" t="n">
-        <v>11.82277159459972</v>
+        <v>1.921200384122455</v>
       </c>
       <c r="E6" t="n">
-        <v>22.03830187623384</v>
+        <v>3.581224054887999</v>
       </c>
       <c r="F6" t="n">
-        <v>12.51736479994342</v>
+        <v>2.034071779990805</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>53.21217780885755</v>
+        <v>8.646978893939352</v>
       </c>
       <c r="D7" t="n">
-        <v>13.07455075905174</v>
+        <v>2.124614498345907</v>
       </c>
       <c r="E7" t="n">
-        <v>22.03830187623384</v>
+        <v>3.581224054887999</v>
       </c>
       <c r="F7" t="n">
-        <v>12.51736479994342</v>
+        <v>2.034071779990805</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.959461396883594</v>
+        <v>1.455912476993584</v>
       </c>
       <c r="D8" t="n">
-        <v>10.20637096922763</v>
+        <v>1.658535282499489</v>
       </c>
       <c r="E8" t="n">
-        <v>22.03830187623384</v>
+        <v>3.581224054887999</v>
       </c>
       <c r="F8" t="n">
-        <v>12.51736479994342</v>
+        <v>2.034071779990805</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
